--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,62 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>销售出库单</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>运单号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>计费重[物流商]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实际运费[物流商]</t>
+    </r>
+  </si>
+  <si>
+    <t>币种</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
@@ -23,10 +79,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -496,138 +559,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,9 +1007,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="18.375" customWidth="1"/>
+    <col min="2" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="17.625" customWidth="1"/>
+    <col min="5" max="5" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -11,17 +11,49 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>销售出库单</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售出库单</t>
+    </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -37,6 +69,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -52,6 +91,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -72,7 +118,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1018,7 +1064,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -91,13 +98,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -108,7 +108,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>实际运费[物流商]</t>
+      <t>费用名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实际运费</t>
     </r>
   </si>
   <si>
@@ -125,7 +139,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +296,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1053,17 +1073,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="5" max="5" width="13.375" customWidth="1"/>
+    <col min="4" max="5" width="17.625" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1076,8 +1096,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
       <rPr>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>币种</t>
+  </si>
+  <si>
+    <t>物流费用</t>
   </si>
 </sst>
 </file>
@@ -1073,8 +1076,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
@@ -1101,6 +1104,11 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="4:4">
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -54,14 +54,16 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*</t>
+      <t>运单</t>
     </r>
     <r>
       <rPr>
@@ -71,7 +73,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>运单号</t>
+      <t>号</t>
     </r>
   </si>
   <si>
@@ -98,6 +100,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -113,6 +122,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -63,17 +63,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>运单</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>号</t>
+      <t>物流跟踪单号</t>
     </r>
   </si>
   <si>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <r>
       <rPr>
@@ -54,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -90,6 +97,30 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>对账</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
@@ -111,6 +142,9 @@
     </r>
   </si>
   <si>
+    <t>预估金额</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -128,14 +162,20 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>实际运费</t>
+      <t>实际金额</t>
     </r>
   </si>
   <si>
     <t>币种</t>
   </si>
   <si>
+    <t>付款</t>
+  </si>
+  <si>
     <t>物流费用</t>
+  </si>
+  <si>
+    <t>退款</t>
   </si>
 </sst>
 </file>
@@ -164,6 +204,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -305,12 +351,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -634,141 +674,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,17 +1125,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="3" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="17.625" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="17.625" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1108,13 +1153,27 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="4:4">
+    <row r="2" spans="4:5">
       <c r="D2" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="4:4">
+      <c r="D3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
       <rPr>
@@ -74,6 +74,12 @@
     </r>
   </si>
   <si>
+    <t>计费重[预估]</t>
+  </si>
+  <si>
+    <t>计费重[物流商]</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -82,21 +88,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>计费重[物流商]</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>*</t>
     </r>
     <r>
@@ -804,7 +795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -812,6 +803,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1125,55 +1119,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="17.625" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="2" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="4:5">
-      <c r="D2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="2" spans="5:6">
       <c r="E2" t="s">
         <v>9</v>
       </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="4:4">
-      <c r="D3" t="s">
-        <v>10</v>
+    <row r="3" spans="5:5">
+      <c r="E3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
@@ -54,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -132,10 +139,18 @@
     </r>
   </si>
   <si>
-    <t>币种</t>
-  </si>
-  <si>
-    <t>物流费用</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1082,8 +1097,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
@@ -1108,13 +1123,8 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="4:4">
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -32,13 +32,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -54,13 +47,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -81,13 +67,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -112,13 +91,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -137,13 +109,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -31,22 +31,17 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <r>
-      <t>*</t>
-    </r>
+    <t>销售出库单</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>销售出库单</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>*</t>
     </r>
     <r>
@@ -67,6 +62,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -91,6 +93,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -109,6 +118,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -764,13 +780,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1100,25 +1116,25 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,19 @@
     </r>
   </si>
   <si>
-    <t>币种</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
   </si>
   <si>
     <t>付款</t>
@@ -1137,7 +1149,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -29,16 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -74,6 +67,12 @@
     </r>
   </si>
   <si>
+    <t>计费重[预估]</t>
+  </si>
+  <si>
+    <t>计费重[物流商]</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -87,12 +86,21 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>对账</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>计费重[物流商]</t>
+      <t>类型</t>
     </r>
   </si>
   <si>
@@ -135,22 +143,42 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>实际运费</t>
+      <t>实际金额</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>币种</t>
     </r>
+  </si>
+  <si>
+    <t>预估金额</t>
+  </si>
+  <si>
+    <t>付款</t>
+  </si>
+  <si>
+    <t>物流费用</t>
+  </si>
+  <si>
+    <t>退款</t>
   </si>
 </sst>
 </file>
@@ -179,6 +207,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -320,12 +354,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -649,141 +677,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1097,27 +1131,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="2" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="7" width="17.625" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1125,6 +1160,28 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="5:6">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="5:5">
+      <c r="E3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -170,6 +177,9 @@
   </si>
   <si>
     <t>预估金额</t>
+  </si>
+  <si>
+    <t>预估币种</t>
   </si>
   <si>
     <t>付款</t>
@@ -1131,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
@@ -1142,7 +1152,7 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,18 +1180,21 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" spans="5:6">
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="5:5">
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -134,13 +134,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -155,14 +148,16 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*</t>
+      <t>实际</t>
     </r>
     <r>
       <rPr>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,28 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>销售出库单</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+  <si>
+    <t>销售出库单</t>
   </si>
   <si>
     <r>
@@ -134,6 +115,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -148,6 +136,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -184,6 +179,111 @@
   </si>
   <si>
     <t>退款</t>
+  </si>
+  <si>
+    <t>BRL</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>KRW</t>
+  </si>
+  <si>
+    <t>MOP</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>THB</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>PLN</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>NZD</t>
+  </si>
+  <si>
+    <t>RUB</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
+    <t>TWD</t>
+  </si>
+  <si>
+    <t>ZAR</t>
+  </si>
+  <si>
+    <t>MYR</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>CZK</t>
+  </si>
+  <si>
+    <t>KES</t>
+  </si>
+  <si>
+    <t>HUF</t>
+  </si>
+  <si>
+    <t>ILS</t>
   </si>
 </sst>
 </file>
@@ -816,13 +916,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1151,28 +1251,28 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1193,6 +1293,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+      <formula1>Sheet2!$A$8:$A$42</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1202,9 +1307,185 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A8:A42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,36 +29,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
-  <si>
-    <t>销售出库单</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流跟踪单号</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+  <si>
+    <t>平台订单号</t>
+  </si>
+  <si>
+    <t>发货单号</t>
+  </si>
+  <si>
+    <t>销售订单号</t>
+  </si>
+  <si>
+    <t>物流跟踪单号</t>
   </si>
   <si>
     <t>计费重[预估]</t>
   </si>
   <si>
     <t>计费重[物流商]</t>
+  </si>
+  <si>
+    <t>包装尺寸长（物流商）</t>
+  </si>
+  <si>
+    <t>包装尺寸宽（物流商）</t>
+  </si>
+  <si>
+    <t>包装尺寸高（物流商）</t>
+  </si>
+  <si>
+    <t>实重（物流商）</t>
   </si>
   <si>
     <r>
@@ -306,13 +306,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1236,34 +1236,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="18.375" customWidth="1"/>
-    <col min="2" max="3" width="16.375" customWidth="1"/>
-    <col min="4" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="7" width="17.625" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="13" width="17.625" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1272,29 +1274,47 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="5:6">
-      <c r="E2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="5:5">
-      <c r="E3" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="K3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:N$1048576">
       <formula1>Sheet2!$A$8:$A$42</formula1>
     </dataValidation>
   </dataValidations>
@@ -1312,177 +1332,177 @@
   <sheetData>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>平台订单号</t>
   </si>
@@ -179,111 +177,6 @@
   </si>
   <si>
     <t>退款</t>
-  </si>
-  <si>
-    <t>BRL</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>GBP</t>
-  </si>
-  <si>
-    <t>HKD</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>JPY</t>
-  </si>
-  <si>
-    <t>KRW</t>
-  </si>
-  <si>
-    <t>MOP</t>
-  </si>
-  <si>
-    <t>PHP</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
-    <t>THB</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>AUD</t>
-  </si>
-  <si>
-    <t>SEK</t>
-  </si>
-  <si>
-    <t>PLN</t>
-  </si>
-  <si>
-    <t>MXN</t>
-  </si>
-  <si>
-    <t>INR</t>
-  </si>
-  <si>
-    <t>AED</t>
-  </si>
-  <si>
-    <t>CHF</t>
-  </si>
-  <si>
-    <t>DKK</t>
-  </si>
-  <si>
-    <t>NOK</t>
-  </si>
-  <si>
-    <t>NZD</t>
-  </si>
-  <si>
-    <t>RUB</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>TRY</t>
-  </si>
-  <si>
-    <t>TWD</t>
-  </si>
-  <si>
-    <t>ZAR</t>
-  </si>
-  <si>
-    <t>MYR</t>
-  </si>
-  <si>
-    <t>VND</t>
-  </si>
-  <si>
-    <t>CZK</t>
-  </si>
-  <si>
-    <t>KES</t>
-  </si>
-  <si>
-    <t>HUF</t>
-  </si>
-  <si>
-    <t>ILS</t>
   </si>
 </sst>
 </file>
@@ -1315,211 +1208,11 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:N$1048576">
-      <formula1>Sheet2!$A$8:$A$42</formula1>
+      <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A8:A42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -1206,11 +1206,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:N$1048576">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>平台订单号</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>预估币种</t>
+  </si>
+  <si>
+    <t>账单确认时间</t>
   </si>
   <si>
     <t>付款</t>
@@ -1129,7 +1132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -1140,9 +1143,11 @@
     <col min="12" max="13" width="17.625" customWidth="1"/>
     <col min="14" max="14" width="13.375" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1191,18 +1196,21 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="K2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="K3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -24,6 +24,38 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+yyyy/MM/dd</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -192,7 +224,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,6 +388,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -808,7 +851,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -819,6 +862,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1207,6 +1253,7 @@
       <c r="L2" t="s">
         <v>18</v>
       </c>
+      <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:17">
       <c r="K3" t="s">
@@ -1214,8 +1261,15 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576">
+      <formula1>36526</formula1>
+      <formula2>401404</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostTemplate.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="Q1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>物流商</t>
+  </si>
   <si>
     <t>平台订单号</t>
   </si>
@@ -1178,23 +1181,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="16.125" customWidth="1"/>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="5" width="16.375" customWidth="1"/>
-    <col min="6" max="11" width="18.5" customWidth="1"/>
-    <col min="12" max="13" width="17.625" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="14.375" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="6" width="16.375" customWidth="1"/>
+    <col min="7" max="12" width="18.5" customWidth="1"/>
+    <col min="13" max="14" width="17.625" customWidth="1"/>
+    <col min="15" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1203,16 +1207,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1224,7 +1228,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1236,33 +1240,36 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
+    <row r="2" spans="1:18">
       <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="4"/>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:17">
-      <c r="K3" t="s">
-        <v>19</v>
+    <row r="3" spans="1:18">
+      <c r="L3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R$1:R$1048576">
       <formula1>36526</formula1>
       <formula2>401404</formula2>
     </dataValidation>
